--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6929.5</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3759.52</v>
+        <v>3767.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tarapacá" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -633,6 +633,67 @@
         <v>3767.53</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1495199-11-CM26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>13606.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
@@ -684,7 +684,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/tarapaca.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
